--- a/apps/BCGcalc/external/RMD/files/About_CalculationTypes_20261030_mod.xlsx
+++ b/apps/BCGcalc/external/RMD/files/About_CalculationTypes_20261030_mod.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/erik_leppo_tetratech_com/Documents/Documents/NCEA_RMN/20261030_BCG_ORWA_Shiny/About_20261030/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc_ORWA\apps\BCGcalc\external\RMD\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C3936570-DC4D-4F25-B402-1B1635260587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{392C2899-47AF-41BA-A737-DEA4D1E4D969}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A1FBB4-6E20-42D6-A2B7-0B60A922C7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8F0F119-7D9A-4972-B615-198140086982}"/>
   </bookViews>
@@ -41,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
-    <t>Hubler et al. 2024</t>
-  </si>
-  <si>
     <t>Citation</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
     <t>report in progress (2026)</t>
   </si>
   <si>
-    <t>BCG report - Stamp 2022; Historic/natural condititions (BCG Level 1) - Hafele et al. 2022</t>
-  </si>
-  <si>
     <t>Exploratory (not published). R code only</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>Published in peer-reviewed article</t>
   </si>
   <si>
-    <t>Robert Wisseman 2019</t>
-  </si>
-  <si>
     <t>Calculates Biological Condition Gradient (BCG) output for the statewide model (v1)</t>
   </si>
   <si>
@@ -116,20 +107,35 @@
     <t>Fish thermal class (2024)</t>
   </si>
   <si>
-    <t>Tetra Tech 2024 (Fernandez and Stamp)</t>
+    <t>BCG report - Stamp 2022 [[Link]](links/Stamp_2022_MariNWBCG.PDF); Historic/natural condititions (BCG Level 1) - Hafele et al. 2022 [[Link]](links/Hafele_2022_HistoricalReport_AppD.PDF)</t>
+  </si>
+  <si>
+    <t>Hubler et al. 2024 [[Link]](links/Hubler2024_MTTI_ThermPref.pdf)</t>
+  </si>
+  <si>
+    <t>Tetra Tech 2024 (Fernandez and Stamp) [[Link]](links/FishThermalClass_20240619.zip)</t>
+  </si>
+  <si>
+    <t>Robert Wisseman 2019 [[Link]](links/BiodiversityIndex_2019.zip)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -179,34 +185,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,107 +560,106 @@
     <col min="1" max="1" width="25.140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="47.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.85546875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7109375" style="1"/>
+    <col min="4" max="4" width="71.85546875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>4</v>
-      </c>
       <c r="D1" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="9" t="s">
         <v>6</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
